--- a/result_gsea/LUAD_FAT1_chip/LUAD_MSigDB_Hallmark_2020/gseapy.phenotype.gsea.report_cleaned.xlsx
+++ b/result_gsea/LUAD_FAT1_chip/LUAD_MSigDB_Hallmark_2020/gseapy.phenotype.gsea.report_cleaned.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.115</t>
+          <t>2.192</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -508,11 +508,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.120</t>
+          <t>0.065</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.033</v>
+        <v>0.017</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -548,21 +548,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2.134</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -598,21 +598,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.005</t>
+          <t>2.077</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.065</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.065</v>
+        <v>0.045</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -648,21 +648,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.001</t>
+          <t>2.037</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -698,21 +698,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.031</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.077</v>
+        <v>0.064</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -748,21 +748,21 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.974</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.108</v>
+        <v>0.092</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>1.967</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.122</v>
+        <v>0.095</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -848,21 +848,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.110</t>
+          <t>0.090</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.156</v>
+        <v>0.125</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -888,45 +888,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Protein Secretion</t>
+          <t>Angiogenesis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.606</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>1.852</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.198</v>
+        <v>0.167</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55/96</t>
+          <t>16/36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>34.23%</t>
+          <t>10.85%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>GOLGA4;IGF2R;CLCN3;SEC24D;ADAM10;GBF1;ARFGEF2;DST;TSPAN8;MON2;DNM1L;ATP1A1;KIF1B;ABCA1;DOP1A;SSPN;OCRL;LMAN1;COG2;AP3B1;VPS4B;RPS6KA3;ATP7A;M6PR;AP1G1;ARFGEF1;SCAMP1;STAM;SEC31A;EGFR;USO1;SH3GL2;SNAP23;RAB22A;YIPF6;TMX1;RAB14;SCRN1;STX7;ZW10;GALC;COPB2;RAB5A;AP2B1;ARFGAP3;ARFIP1;TMED10;SGMS1;COPB1;MAPK1;ANP32E;TMED2;PAM;ARCN1;CLTC</t>
+          <t>COL5A2;VCAN;STC1;JAG1;POSTN;FGFR1;COL3A1;VAV2;TNFRSF21;ITGAV;THBD;FSTL1;SERPINA5;CCND2;MSX1;PDGFA</t>
         </is>
       </c>
     </row>
@@ -938,45 +938,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IL-2/STAT5 Signaling</t>
+          <t>Protein Secretion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>0.495</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.770</t>
+          <t>1.838</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.229</v>
+        <v>0.174</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>76/198</t>
+          <t>55/96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19.90%</t>
+          <t>34.23%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MYO1E;HIPK2;ITGA6;TNFSF11;ADAM19;UCK2;IL1R2;CDCP1;LIF;IGF1R;POU2F1;IGF2R;PHLDA1;HUWE1;AHNAK;BCL2;NCOA3;SYT11;IL18R1;RORA;FURIN;HK2;IRF6;BMPR2;ENPP1;SLC2A3;GABARAPL1;MXD1;PLEC;TNFRSF21;ITGAV;CYFIP1;LCLAT1;CKAP4;BMP2;TWSG1;SNX9;EMP1;MYC;PNP;NCS1;F2RL2;CCND2;COL6A1;PTCH1;ODC1;SPRY4;ITIH5;IKZF4;PRKCH;SCN9A;TIAM1;CDC6;RHOH;CASP3;MAFF;PLAGL1;SWAP70;DENND5A;ABCB1;P4HA1;RGS16;IL2RA;IL2RB;ETFBKMT;KLF6;TGM2;CA2;IKZF2;CD44;SELP;GBP4;LRIG1;SPRED2;IL4R;NOP2</t>
+          <t>GOLGA4;IGF2R;CLCN3;SEC24D;ADAM10;GBF1;ARFGEF2;DST;TSPAN8;MON2;DNM1L;ATP1A1;KIF1B;ABCA1;DOP1A;SSPN;OCRL;LMAN1;COG2;AP3B1;VPS4B;RPS6KA3;ATP7A;M6PR;AP1G1;ARFGEF1;SCAMP1;STAM;SEC31A;EGFR;USO1;SH3GL2;SNAP23;RAB22A;YIPF6;TMX1;RAB14;SCRN1;STX7;ZW10;GALC;COPB2;RAB5A;AP2B1;ARFGAP3;ARFIP1;TMED10;SGMS1;COPB1;MAPK1;ANP32E;TMED2;PAM;ARCN1;CLTC</t>
         </is>
       </c>
     </row>
@@ -988,45 +988,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Notch Signaling</t>
+          <t>IL-2/STAT5 Signaling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>0.494</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>1.823</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.236</v>
+        <v>0.185</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>76/198</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20.95%</t>
+          <t>19.90%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>JAG1;NOTCH1;NOTCH3;NOTCH2;FZD7;DTX1;TCF7L2;HEYL;FZD1;FBXW11;CCND1;SAP30;WNT2;DLL1;FZD5;PRKCA</t>
+          <t>MYO1E;HIPK2;ITGA6;TNFSF11;ADAM19;UCK2;IL1R2;CDCP1;LIF;IGF1R;POU2F1;IGF2R;PHLDA1;HUWE1;AHNAK;BCL2;NCOA3;SYT11;IL18R1;RORA;FURIN;HK2;IRF6;BMPR2;ENPP1;SLC2A3;GABARAPL1;MXD1;PLEC;TNFRSF21;ITGAV;CYFIP1;LCLAT1;CKAP4;BMP2;TWSG1;SNX9;EMP1;MYC;PNP;NCS1;F2RL2;CCND2;COL6A1;PTCH1;ODC1;SPRY4;ITIH5;IKZF4;PRKCH;SCN9A;TIAM1;CDC6;RHOH;CASP3;MAFF;PLAGL1;SWAP70;DENND5A;ABCB1;P4HA1;RGS16;IL2RA;IL2RB;ETFBKMT;KLF6;TGM2;CA2;IKZF2;CD44;SELP;GBP4;LRIG1;SPRED2;IL4R;NOP2</t>
         </is>
       </c>
     </row>
@@ -1038,45 +1038,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Angiogenesis</t>
+          <t>Notch Signaling</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.749</t>
+          <t>1.808</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.150</t>
+          <t>0.113</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.248</v>
+        <v>0.197</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16/36</t>
+          <t>16/32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.85%</t>
+          <t>20.95%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>COL5A2;VCAN;STC1;JAG1;POSTN;FGFR1;COL3A1;VAV2;TNFRSF21;ITGAV;THBD;FSTL1;SERPINA5;CCND2;MSX1;PDGFA</t>
+          <t>JAG1;NOTCH1;NOTCH3;NOTCH2;FZD7;DTX1;TCF7L2;HEYL;FZD1;FBXW11;CCND1;SAP30;WNT2;DLL1;FZD5;PRKCA</t>
         </is>
       </c>
     </row>
@@ -1088,45 +1088,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unfolded Protein Response</t>
+          <t>Estrogen Response Late</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>1.772</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.25</v>
+        <v>0.236</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>49/112</t>
+          <t>62/197</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.57%</t>
+          <t>14.90%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>STC2;DCP1A;SLC7A5;ERO1A;EDC4;CNOT6;ERN1;HYOU1;CNOT2;EIF2AK3;EIF4E;ATF6;DCTN1;SLC1A4;NOP14;SHC1;NOLC1;MTREX;IGFBP1;FKBP14;EXOC2;DNAJC3;NFYB;CNOT4;MTHFD2;SEC31A;KIF5B;IARS1;SPCS3;SDAD1;HSPA9;EIF4G1;ALDH18A1;PDIA5;XPOT;TATDN2;PDIA6;EDEM1;TARS1;DCP2;SSR1;BAG3;HSP90B1;EIF2S1;CEBPG;SLC30A5;GEMIN4;TUBB2A;WFS1</t>
+          <t>DLG5;CA12;TFF1;ABHD2;SLC24A3;CPE;NRIP1;ATP2B4;FLNB;FARP1;LARGE1;AFF1;LAMC2;SLC26A2;SLC16A1;BCL2;GJB3;RET;TRIM29;KLF4;HR;PLK4;RABEP1;SLC7A5;KLK10;SERPINA3;HSPA4L;STIL;DYNLT3;PDLIM3;FRK;TMPRSS3;SERPINA5;TPBG;SLC1A4;CELSR2;GAL;NCOR2;SORD;JAK1;SCUBE2;ASCL1;MYOF;NPY1R;SCARB1;CCND1;TOP2A;TIAM1;EGR3;KLK11;UGDH;CDC6;CYP26B1;RAB31;TFF3;KIF20A;PRSS23;DNAJC12;JAK2;OPN3;FKBP4;CHPT1</t>
         </is>
       </c>
     </row>
@@ -1138,45 +1138,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Estrogen Response Late</t>
+          <t>Apical Junction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>1.765</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.255</v>
+        <v>0.242</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>62/197</t>
+          <t>70/197</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14.90%</t>
+          <t>16.69%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DLG5;CA12;TFF1;ABHD2;SLC24A3;CPE;NRIP1;ATP2B4;FLNB;FARP1;LARGE1;AFF1;LAMC2;SLC26A2;SLC16A1;BCL2;GJB3;RET;TRIM29;KLF4;HR;PLK4;RABEP1;SLC7A5;KLK10;SERPINA3;HSPA4L;STIL;DYNLT3;PDLIM3;FRK;TMPRSS3;SERPINA5;TPBG;SLC1A4;CELSR2;GAL;NCOR2;SORD;JAK1;SCUBE2;ASCL1;MYOF;NPY1R;SCARB1;CCND1;TOP2A;TIAM1;EGR3;KLK11;UGDH;CDC6;CYP26B1;RAB31;TFF3;KIF20A;PRSS23;DNAJC12;JAK2;OPN3;FKBP4;CHPT1</t>
+          <t>VCAN;AKT3;JAM3;RASA1;FLNC;ADAMTS5;IRS1;LAMA3;FBN1;ITGA2;NF1;ITGB1;PCDH1;EPB41L2;CDH6;CDH11;MYH10;NECTIN1;LAMC2;MAP3K20;VCL;SLIT2;PPP2R2C;LAMB3;PARD6G;ADAM9;VWF;SHROOM2;TJP1;PARVA;PIK3CB;COL17A1;COL16A1;VAV2;ACTN1;DMP1;NEXN;GNAI1;ADAM23;CD34;VCAM1;ITGB4;PKD1;THY1;ACTG2;CDH8;LIMA1;CD209;SHC1;MMP2;CLDN14;DLG1;FSCN1;CNTN1;SIRPA;TGFBI;BMP1;NLGN3;CD276;MMP9;EGFR;TRO;FYB1;MYH9;PTEN;DSC3;NFASC;TNFRSF11B;NRXN2;NEGR1</t>
         </is>
       </c>
     </row>
@@ -1188,45 +1188,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Apical Junction</t>
+          <t>Wnt-beta Catenin Signaling</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.480</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>1.760</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.272</v>
+        <v>0.246</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>70/197</t>
+          <t>24/42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16.69%</t>
+          <t>26.17%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>VCAN;AKT3;JAM3;RASA1;FLNC;ADAMTS5;IRS1;LAMA3;FBN1;ITGA2;NF1;ITGB1;PCDH1;EPB41L2;CDH6;CDH11;MYH10;NECTIN1;LAMC2;MAP3K20;VCL;SLIT2;PPP2R2C;LAMB3;PARD6G;ADAM9;VWF;SHROOM2;TJP1;PARVA;PIK3CB;COL17A1;COL16A1;VAV2;ACTN1;DMP1;NEXN;GNAI1;ADAM23;CD34;VCAM1;ITGB4;PKD1;THY1;ACTG2;CDH8;LIMA1;CD209;SHC1;MMP2;CLDN14;DLG1;FSCN1;CNTN1;SIRPA;TGFBI;BMP1;NLGN3;CD276;MMP9;EGFR;TRO;FYB1;MYH9;PTEN;DSC3;NFASC;TNFRSF11B;NRXN2;NEGR1</t>
+          <t>JAG1;NOTCH1;NKD1;DKK1;MAML1;GNAI1;NOTCH4;LEF1;ADAM17;FZD1;HEY2;MYC;NCOR2;CCND2;PTCH1;HDAC2;TCF7;DLL1;JAG2;CTNNB1;NUMB;RBPJ;WNT5B;TP53</t>
         </is>
       </c>
     </row>
@@ -1238,45 +1238,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wnt-beta Catenin Signaling</t>
+          <t>KRAS Signaling Up</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.721</t>
+          <t>1.747</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.130</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.275</v>
+        <v>0.261</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24/42</t>
+          <t>90/200</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26.17%</t>
+          <t>25.38%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>JAG1;NOTCH1;NKD1;DKK1;MAML1;GNAI1;NOTCH4;LEF1;ADAM17;FZD1;HEY2;MYC;NCOR2;CCND2;PTCH1;HDAC2;TCF7;DLL1;JAG2;CTNNB1;NUMB;RBPJ;WNT5B;TP53</t>
+          <t>TRIB2;INHBA;AKAP12;SOX9;ADGRA2;ITGA2;CPE;DNMBP;NIN;AMMECR1;LIF;MTMR10;GFPT2;ANXA10;CCL20;PRDM1;PRKG2;GPRC5B;ANKH;PTGS2;ADGRL4;SPON1;EPB41L3;PTPRR;PRRX1;ANO1;HKDC1;ITGBL1;ETS1;KLF4;CBL;FLT4;CCSER2;SERPINA3;CFH;SATB1;HOXD11;ERO1A;TMEM158;BTBD3;AVL9;ADAM17;USH1C;RELN;PTCD2;MAP7;BMP2;TNFAIP3;STRN;EMP1;MMP10;CCND2;MAP3K1;F2RL1;F13A1;DCBLD2;TSPAN1;PLEK2;USP12;EVI5;GUCY1A1;MMP9;ABCB1;DOCK2;ACE;DUSP6;PLVAP;RGS16;ANGPTL4;HBEGF;PEG3;PLAUR;CA2;IGF2;VWA5A;IL7R;NR1H4;ETV5;TFPI;WNT7A;CMKLR1;KIF5C;IL1B;ALDH1A3;H2BC3;PECAM1;ADAM8;IGFBP3;NRP1;CBR4</t>
         </is>
       </c>
     </row>
@@ -1288,45 +1288,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KRAS Signaling Up</t>
+          <t>Unfolded Protein Response</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1.742</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.113</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.29</v>
+        <v>0.265</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>90/200</t>
+          <t>49/112</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25.38%</t>
+          <t>27.57%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>TRIB2;INHBA;AKAP12;SOX9;ADGRA2;ITGA2;CPE;DNMBP;NIN;AMMECR1;LIF;MTMR10;GFPT2;ANXA10;CCL20;PRDM1;PRKG2;GPRC5B;ANKH;PTGS2;ADGRL4;SPON1;EPB41L3;PTPRR;PRRX1;ANO1;HKDC1;ITGBL1;ETS1;KLF4;CBL;FLT4;CCSER2;SERPINA3;CFH;SATB1;HOXD11;ERO1A;TMEM158;BTBD3;AVL9;ADAM17;USH1C;RELN;PTCD2;MAP7;BMP2;TNFAIP3;STRN;EMP1;MMP10;CCND2;MAP3K1;F2RL1;F13A1;DCBLD2;TSPAN1;PLEK2;USP12;EVI5;GUCY1A1;MMP9;ABCB1;DOCK2;ACE;DUSP6;PLVAP;RGS16;ANGPTL4;HBEGF;PEG3;PLAUR;CA2;IGF2;VWA5A;IL7R;NR1H4;ETV5;TFPI;WNT7A;CMKLR1;KIF5C;IL1B;ALDH1A3;H2BC3;PECAM1;ADAM8;IGFBP3;NRP1;CBR4</t>
+          <t>STC2;DCP1A;SLC7A5;ERO1A;EDC4;CNOT6;ERN1;HYOU1;CNOT2;EIF2AK3;EIF4E;ATF6;DCTN1;SLC1A4;NOP14;SHC1;NOLC1;MTREX;IGFBP1;FKBP14;EXOC2;DNAJC3;NFYB;CNOT4;MTHFD2;SEC31A;KIF5B;IARS1;SPCS3;SDAD1;HSPA9;EIF4G1;ALDH18A1;PDIA5;XPOT;TATDN2;PDIA6;EDEM1;TARS1;DCP2;SSR1;BAG3;HSP90B1;EIF2S1;CEBPG;SLC30A5;GEMIN4;TUBB2A;WFS1</t>
         </is>
       </c>
     </row>
@@ -1348,21 +1348,21 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>1.708</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0.048</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.301</v>
+        <v>0.285</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1388,45 +1388,45 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>p53 Pathway</t>
+          <t>mTORC1 Signaling</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>0.431</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.641</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.404</v>
+        <v>0.344</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>62/199</t>
+          <t>69/199</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21.45%</t>
+          <t>22.51%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KIF13B;PITPNC1;CCNK;CDH13;POM121;SERPINB5;SLC7A11;NOTCH1;LIF;PTPN14;PLK2;XPC;FBXW7;F2R;SLC35D1;APAF1;ZMAT3;ELP1;CDK5R1;AEN;WWP1;KLF4;TAX1BP3;SP1;TGFA;MXD1;KLK8;HSPA4L;FOXO3;CCP110;ERCC5;ITGB4;BMP2;MDM2;CDKN2AIP;CCND2;ZNF365;TM7SF3;TP63;KRT17;DGKA;NOL8;PDGFA;RB1;VDR;CYFIP2;IER3;GPX2;PTPRE;RGS16;HBEGF;PPM1D;EPHA2;ADA;JAG2;NHLH2;VWA5A;RNF19B;CDKN1A;NDRG1;CD82;FOS</t>
+          <t>IGFBP5;STC1;EGLN3;CYP51A1;SLC7A11;GSK3B;AK4;NAMPT;SLC2A1;ELOVL6;ATP2A2;HMGCR;VLDLR;PLOD2;ALDOA;LDLR;ACSL3;HK2;SLC2A3;FADS2;PLK1;SLC7A5;GBE1;ERO1A;MLLT11;SLC6A6;ADIPOR2;DHFR;TBK1;SLC1A4;HMGCS1;PNP;MCM2;SORD;NUP205;ACACA;CDC25A;M6PR;MCM4;PDK1;AURKA;TFRC;MTHFD2;GMPS;RRM2;EPRS1;USO1;P4HA1;UNG;HSPA9;GTF2H1;TXNRD1;HSPA4;FADS1;SQLE;CANX;HSPD1;CDKN1A;ACLY;GOT1;EDEM1;LDHA;RDH11;BUB1;PITPNB;SCD;BCAT1;SSR1;BHLHE40</t>
         </is>
       </c>
     </row>
@@ -1438,45 +1438,45 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mTORC1 Signaling</t>
+          <t>PI3K/AKT/mTOR  Signaling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.610</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.412</v>
+        <v>0.379</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>69/199</t>
+          <t>43/105</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22.51%</t>
+          <t>32.43%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IGFBP5;STC1;EGLN3;CYP51A1;SLC7A11;GSK3B;AK4;NAMPT;SLC2A1;ELOVL6;ATP2A2;HMGCR;VLDLR;PLOD2;ALDOA;LDLR;ACSL3;HK2;SLC2A3;FADS2;PLK1;SLC7A5;GBE1;ERO1A;MLLT11;SLC6A6;ADIPOR2;DHFR;TBK1;SLC1A4;HMGCS1;PNP;MCM2;SORD;NUP205;ACACA;CDC25A;M6PR;MCM4;PDK1;AURKA;TFRC;MTHFD2;GMPS;RRM2;EPRS1;USO1;P4HA1;UNG;HSPA9;GTF2H1;TXNRD1;HSPA4;FADS1;SQLE;CANX;HSPD1;CDKN1A;ACLY;GOT1;EDEM1;LDHA;RDH11;BUB1;PITPNB;SCD;BCAT1;SSR1;BHLHE40</t>
+          <t>SMAD2;PRKAA2;GSK3B;PTPN11;SLC2A1;PIKFYVE;PITX2;MAP2K6;RPTOR;PLCB1;MAPK8;RAF1;EIF4E;TBK1;ACACA;RPS6KA3;PDK1;ATF1;TIAM1;ITPR2;EGFR;CAB39;PTEN;GNGT1;AKT1;CAMK4;PRKAR2A;RIPK1;CDKN1A;MAPK9;HSP90B1;MAP2K3;MAP3K7;ACTR2;TRAF2;TSC2;MAPKAP1;YWHAB;PPP2R1B;PRKCB;CDK1;RALB;MAPK1</t>
         </is>
       </c>
     </row>
@@ -1488,45 +1488,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PI3K/AKT/mTOR  Signaling</t>
+          <t>Apical Surface</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.470</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.568</t>
+          <t>1.562</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>0.204</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>43/105</t>
+          <t>24/44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>32.43%</t>
+          <t>30.46%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SMAD2;PRKAA2;GSK3B;PTPN11;SLC2A1;PIKFYVE;PITX2;MAP2K6;RPTOR;PLCB1;MAPK8;RAF1;EIF4E;TBK1;ACACA;RPS6KA3;PDK1;ATF1;TIAM1;ITPR2;EGFR;CAB39;PTEN;GNGT1;AKT1;CAMK4;PRKAR2A;RIPK1;CDKN1A;MAPK9;HSP90B1;MAP2K3;MAP3K7;ACTR2;TRAF2;TSC2;MAPKAP1;YWHAB;PPP2R1B;PRKCB;CDK1;RALB;MAPK1</t>
+          <t>SULF2;ATP8B1;NCOA6;ADAM10;SHROOM2;EFNA5;PCSK9;ADIPOR2;THY1;GAS1;BRCA1;DCBLD2;AFAP1L2;IL2RB;MDGA1;PLAUR;SRPX;NTNG1;APP;GATA3;B4GALT1;LYPD3;PKHD1;RHCG</t>
         </is>
       </c>
     </row>
@@ -1538,27 +1538,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>G2-M Checkpoint</t>
+          <t>p53 Pathway</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.381</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.120</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>113/198</t>
+          <t>62/199</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25.68%</t>
+          <t>21.45%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>STAG1;ATRX;MKI67;SLC7A1;UCK2;KIF20B;CENPF;SLC12A2;WRN;RASAL2;SMAD3;KNL1;MAP3K20;NOTCH2;CENPE;CTCF;PDS5B;FOXN3;NSD2;SMC2;MEIS2;SMC1A;KIF11;CCNT1;LMNB1;EFNA5;PLK4;INCENP;CASP8AP2;PBK;CUL3;SLC38A1;PLK1;SLC7A5;G3BP1;PURA;RACGAP1;STIL;ABL1;CCNA2;POLE;LBR;NUP98;ESPL1;PRMT5;PAFAH1B1;KIF4A;KIF23;HIF1A;EXO1;SMARCC1;MEIS1;E2F3;MYC;RBL1;MCM2;TPX2;NOLC1;NUP50;ODC1;POLQ;CDC27;CDC25A;CHAF1A;TLE3;CCND1;FBXO5;AURKA;TOP2A;HMMR;TMPO;MAD2L1;SYNCRIP;MARCKS;CDC6;BRCA2;KPNB1;SS18;LIG3;CHEK1;SAP30;KIF5B;NEK2;KIF15;FANCC;PTTG3P;HOXC10;KMT5A;CCNB2;ARID4A;HNRNPU;SMC4;RAD54L;TNPO2;YTHDC1;ATF5;SQLE;NDC80;CUL5;BUB1;PRC1;KPNA2;EZH2;RAD23B;MNAT1;E2F2;XPO1;GSPT1;HSPA8;UPF1;CCNF;NUMA1;RBM14</t>
+          <t>KIF13B;PITPNC1;CCNK;CDH13;POM121;SERPINB5;SLC7A11;NOTCH1;LIF;PTPN14;PLK2;XPC;FBXW7;F2R;SLC35D1;APAF1;ZMAT3;ELP1;CDK5R1;AEN;WWP1;KLF4;TAX1BP3;SP1;TGFA;MXD1;KLK8;HSPA4L;FOXO3;CCP110;ERCC5;ITGB4;BMP2;MDM2;CDKN2AIP;CCND2;ZNF365;TM7SF3;TP63;KRT17;DGKA;NOL8;PDGFA;RB1;VDR;CYFIP2;IER3;GPX2;PTPRE;RGS16;HBEGF;PPM1D;EPHA2;ADA;JAG2;NHLH2;VWA5A;RNF19B;CDKN1A;NDRG1;CD82;FOS</t>
         </is>
       </c>
     </row>
@@ -1588,45 +1588,45 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apical Surface</t>
+          <t>TNF-alpha Signaling via NF-kB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.470</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.537</t>
+          <t>1.550</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.455</v>
+        <v>0.444</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24/44</t>
+          <t>77/198</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30.46%</t>
+          <t>21.45%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SULF2;ATP8B1;NCOA6;ADAM10;SHROOM2;EFNA5;PCSK9;ADIPOR2;THY1;GAS1;BRCA1;DCBLD2;AFAP1L2;IL2RB;MDGA1;PLAUR;SRPX;NTNG1;APP;GATA3;B4GALT1;LYPD3;PKHD1;RHCG</t>
+          <t>DUSP4;ATP2B1;SERPINB8;JAG1;INHBA;PDLIM5;NFAT5;PMEPA1;IRS2;LIF;GFPT2;PLK2;SMAD3;NAMPT;PHLDA1;CCL20;LAMB3;F3;PTGS2;FUT4;PDE4B;KLF4;LDLR;SERPINE1;FJX1;SLC2A3;MXD1;REL;ABCA1;TNFAIP6;KYNU;NFKB1;ACKR3;BMP2;TNFAIP3;MYC;ETS2;GEM;FOSL2;F2RL1;CXCL1;CCND1;EGR1;TNC;EGR3;MARCKS;DUSP5;PANX1;MAFF;PLPP3;NR4A2;DENND5A;SERPINB2;IER3;PTPRE;FOSL1;HBEGF;ZBTB10;TNFAIP8;KLF9;ICOSLG;KLF6;PLAUR;CXCL3;EGR2;CD44;B4GALT5;KDM6B;KLF10;NR4A1;IL6;RNF19B;IL7R;CDKN1A;GCH1;KLF2;FOS</t>
         </is>
       </c>
     </row>
@@ -1638,45 +1638,45 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TNF-alpha Signaling via NF-kB</t>
+          <t>G2-M Checkpoint</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.111</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.188</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.464</v>
+        <v>0.445</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>77/198</t>
+          <t>113/198</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21.45%</t>
+          <t>25.68%</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DUSP4;ATP2B1;SERPINB8;JAG1;INHBA;PDLIM5;NFAT5;PMEPA1;IRS2;LIF;GFPT2;PLK2;SMAD3;NAMPT;PHLDA1;CCL20;LAMB3;F3;PTGS2;FUT4;PDE4B;KLF4;LDLR;SERPINE1;FJX1;SLC2A3;MXD1;REL;ABCA1;TNFAIP6;KYNU;NFKB1;ACKR3;BMP2;TNFAIP3;MYC;ETS2;GEM;FOSL2;F2RL1;CXCL1;CCND1;EGR1;TNC;EGR3;MARCKS;DUSP5;PANX1;MAFF;PLPP3;NR4A2;DENND5A;SERPINB2;IER3;PTPRE;FOSL1;HBEGF;ZBTB10;TNFAIP8;KLF9;ICOSLG;KLF6;PLAUR;CXCL3;EGR2;CD44;B4GALT5;KDM6B;KLF10;NR4A1;IL6;RNF19B;IL7R;CDKN1A;GCH1;KLF2;FOS</t>
+          <t>STAG1;ATRX;MKI67;SLC7A1;UCK2;KIF20B;CENPF;SLC12A2;WRN;RASAL2;SMAD3;KNL1;MAP3K20;NOTCH2;CENPE;CTCF;PDS5B;FOXN3;NSD2;SMC2;MEIS2;SMC1A;KIF11;CCNT1;LMNB1;EFNA5;PLK4;INCENP;CASP8AP2;PBK;CUL3;SLC38A1;PLK1;SLC7A5;G3BP1;PURA;RACGAP1;STIL;ABL1;CCNA2;POLE;LBR;NUP98;ESPL1;PRMT5;PAFAH1B1;KIF4A;KIF23;HIF1A;EXO1;SMARCC1;MEIS1;E2F3;MYC;RBL1;MCM2;TPX2;NOLC1;NUP50;ODC1;POLQ;CDC27;CDC25A;CHAF1A;TLE3;CCND1;FBXO5;AURKA;TOP2A;HMMR;TMPO;MAD2L1;SYNCRIP;MARCKS;CDC6;BRCA2;KPNB1;SS18;LIG3;CHEK1;SAP30;KIF5B;NEK2;KIF15;FANCC;PTTG3P;HOXC10;KMT5A;CCNB2;ARID4A;HNRNPU;SMC4;RAD54L;TNPO2;YTHDC1;ATF5;SQLE;NDC80;CUL5;BUB1;PRC1;KPNA2;EZH2;RAD23B;MNAT1;E2F2;XPO1;GSPT1;HSPA8;UPF1;CCNF;NUMA1;RBM14</t>
         </is>
       </c>
     </row>
@@ -1688,45 +1688,45 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>heme Metabolism</t>
+          <t>Complement</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.508</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.102</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.525</v>
+        <v>0.479</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>64/199</t>
+          <t>52/200</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>24.17%</t>
+          <t>13.89%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SMOX;SLC7A11;TNRC6B;NUDT4;BMP2K;SLC6A8;CLCN3;SLC2A1;ANK1;BTRC;MOCOS;RANBP10;RNF123;NR3C1;FOXJ2;ARHGEF12;KLF3;SEC14L1;KHNYN;AGPAT4;FOXO3;MARCHF8;EPB41;BACH1;FECH;XK;TNS1;CDC27;XPO7;LRP10;KDM7A;MFHAS1;ELL2;ADD2;NFE2L1;DCAF10;TFRC;TRIM10;IGSF3;GMPS;HBBP1;DAAM1;MARK3;GCLM;GAPVD1;ADD1;USP15;CAST;TSPO2;P4HA2;TFDP2;NNT;CA2;VEZF1;DCUN1D1;RHAG;SLC30A1;E2F2;SPTA1;H4C3;ERMAP;MXI1;MINPP1;LPIN2</t>
+          <t>CDH13;F5;COL4A2;LRP1;ZEB1;USP8;DYRK2;KIF2A;PIK3CA;PRDM4;F3;FN1;ADAM9;HNF4A;ZFPM2;MMP12;CDK5R1;PDGFB;PLA2G4A;SERPINE1;DGKG;NOTCH4;DGKH;CFH;PCSK9;SH2B3;KYNU;RAF1;TNFAIP3;VCPIP1;KLK1;GNB4;CBLB;TIMP2;MMP14;GNG2;XPNPEP1;CXCL1;DOCK9;GPD2;GMFB;PCLO;RNF4;L3MBTL4;DUSP5;CR1;CASP3;MAFF;PREP;USP14;SERPINB2;JAK2</t>
         </is>
       </c>
     </row>
@@ -1738,45 +1738,45 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apoptosis</t>
+          <t>heme Metabolism</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.440</t>
+          <t>1.452</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.251</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.55</v>
+        <v>0.533</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>52/160</t>
+          <t>64/199</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25.08%</t>
+          <t>24.17%</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ROCK1;PDGFRB;IGF2R;F2R;ANKH;CREBBP;TGFB2;DNM1L;LEF1;SATB1;MADD;AVPR1A;PLPPR4;SPTAN1;BMP2;BRCA1;BCL2L11;BCL2L2;TIMP2;EMP1;XIAP;CCND2;MMP2;SLC20A1;CCND1;CYLD;DNAJC3;TOP2A;EGR3;CASP3;SMAD7;RNASEL;IER3;FEZ1;ENO2;HGF;TGFBR3;TIMP3;WEE1;ADD1;CASP2;CD44;IL6;CTNNB1;CDKN1A;GCH1;PSEN1;PMAIP1;IL1B;ETF1;APP;VDAC2</t>
+          <t>SMOX;SLC7A11;TNRC6B;NUDT4;BMP2K;SLC6A8;CLCN3;SLC2A1;ANK1;BTRC;MOCOS;RANBP10;RNF123;NR3C1;FOXJ2;ARHGEF12;KLF3;SEC14L1;KHNYN;AGPAT4;FOXO3;MARCHF8;EPB41;BACH1;FECH;XK;TNS1;CDC27;XPO7;LRP10;KDM7A;MFHAS1;ELL2;ADD2;NFE2L1;DCAF10;TFRC;TRIM10;IGSF3;GMPS;HBBP1;DAAM1;MARK3;GCLM;GAPVD1;ADD1;USP15;CAST;TSPO2;P4HA2;TFDP2;NNT;CA2;VEZF1;DCUN1D1;RHAG;SLC30A1;E2F2;SPTA1;H4C3;ERMAP;MXI1;MINPP1;LPIN2</t>
         </is>
       </c>
     </row>
@@ -1788,45 +1788,45 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Complement</t>
+          <t>Apoptosis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.556</v>
+        <v>0.541</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>52/200</t>
+          <t>52/160</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.89%</t>
+          <t>25.08%</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CDH13;F5;COL4A2;LRP1;ZEB1;USP8;DYRK2;KIF2A;PIK3CA;PRDM4;F3;FN1;ADAM9;HNF4A;ZFPM2;MMP12;CDK5R1;PDGFB;PLA2G4A;SERPINE1;DGKG;NOTCH4;DGKH;CFH;PCSK9;SH2B3;KYNU;RAF1;TNFAIP3;VCPIP1;KLK1;GNB4;CBLB;TIMP2;MMP14;GNG2;XPNPEP1;CXCL1;DOCK9;GPD2;GMFB;PCLO;RNF4;L3MBTL4;DUSP5;CR1;CASP3;MAFF;PREP;USP14;SERPINB2;JAK2</t>
+          <t>ROCK1;PDGFRB;IGF2R;F2R;ANKH;CREBBP;TGFB2;DNM1L;LEF1;SATB1;MADD;AVPR1A;PLPPR4;SPTAN1;BMP2;BRCA1;BCL2L11;BCL2L2;TIMP2;EMP1;XIAP;CCND2;MMP2;SLC20A1;CCND1;CYLD;DNAJC3;TOP2A;EGR3;CASP3;SMAD7;RNASEL;IER3;FEZ1;ENO2;HGF;TGFBR3;TIMP3;WEE1;ADD1;CASP2;CD44;IL6;CTNNB1;CDKN1A;GCH1;PSEN1;PMAIP1;IL1B;ETF1;APP;VDAC2</t>
         </is>
       </c>
     </row>
@@ -1848,21 +1848,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.140</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.284</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.598</v>
+        <v>0.588</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1898,21 +1898,21 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.320</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.634</v>
+        <v>0.617</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1948,21 +1948,21 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.330</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.669</v>
+        <v>0.646</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1998,21 +1998,21 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.290</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.370</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.704</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.246</t>
+          <t>1.287</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.727</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2098,21 +2098,21 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1.248</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.230</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.734</v>
+        <v>0.72</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2138,45 +2138,45 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Myc Targets V2</t>
+          <t>Spermatogenesis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.207</t>
+          <t>1.176</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.744</v>
+        <v>0.773</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17/57</t>
+          <t>40/133</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>21.93%</t>
+          <t>22.20%</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>UTP20;TCOF1;PLK4;HK2;PLK1;MYC;PPRC1;SORD;NOLC1;MCM4;WDR43;UNG;PRMT3;NOP2;HSPD1;RRP12;GRWD1</t>
+          <t>JAM3;MTNR1A;SLC12A2;IDE;ZC3H14;DCC;AGFG1;MTOR;NOS1;HSPA4L;SIRT1;TOPBP1;MAP7;CSNK2A2;STRBP;GPR182;PIAS2;LPIN1;AURKA;NEK2;PRM2;CLPB;ACE;SLC2A5;ADAD1;CCNB2;DNAJB8;NPY5R;ADCYAP1;PAPOLB;CAMK4;PRKAR2A;TLE4;NCAPH;BUB1;NF2;BRAF;EZH2;IL12RB2;GRM8</t>
         </is>
       </c>
     </row>
@@ -2188,45 +2188,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oxidative Phosphorylation</t>
+          <t>Myc Targets V2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-0.311</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-1.184</t>
+          <t>1.171</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.7702429149797571</v>
+        <v>0.775</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>75/200</t>
+          <t>17/57</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17.04%</t>
+          <t>21.93%</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ATP5PO;CYB5A;ATP6V0C;NDUFA2;UQCR10;NDUFB8;NDUFS7;NDUFS8;ATP5MG;NDUFB1;MRPS15;POLR2F;MPC1;ATP5MF;TIMM8B;MTRF1;COX5B;ATP5ME;NDUFB7;NDUFB2;UQCR11;ATP6V1F;ECI1;ETFB;PHYH;ATP6V0B;GPX4;ATP5F1D;SURF1;NDUFA3;TIMM10;ECH1;ATP5MC1;BDH2;LDHB;NDUFA9;NDUFA7;MRPL34;ATP5PF;NDUFS6;ATP5PD;NDUFS3;NDUFB6;NDUFB5;SDHA;COX6C;TCIRG1;MRPL11;UQCRQ;COX8A;HTRA2;NDUFA6;NDUFA4;MTRR;NQO2;ATP5F1E;NDUFV1;RHOT2;SDHD;COX7A2;COX6B1;COX7B;NDUFB4;ACAT1;MRPS12;COX4I1;NDUFC2;HSD17B10;CYC1;COX6A1;ACADVL;FDX1;NDUFA1;SDHB;SUCLG1</t>
+          <t>UTP20;TCOF1;PLK4;HK2;PLK1;MYC;PPRC1;SORD;NOLC1;MCM4;WDR43;UNG;PRMT3;NOP2;HSPD1;RRP12;GRWD1</t>
         </is>
       </c>
     </row>
@@ -2238,45 +2238,45 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spermatogenesis</t>
+          <t>Oxidative Phosphorylation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>-0.311</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>-1.168</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>0.350</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.637</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.76</v>
+        <v>0.8014256619144603</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>40/133</t>
+          <t>75/200</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22.20%</t>
+          <t>17.04%</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>JAM3;MTNR1A;SLC12A2;IDE;ZC3H14;DCC;AGFG1;MTOR;NOS1;HSPA4L;SIRT1;TOPBP1;MAP7;CSNK2A2;STRBP;GPR182;PIAS2;LPIN1;AURKA;NEK2;PRM2;CLPB;ACE;SLC2A5;ADAD1;CCNB2;DNAJB8;NPY5R;ADCYAP1;PAPOLB;CAMK4;PRKAR2A;TLE4;NCAPH;BUB1;NF2;BRAF;EZH2;IL12RB2;GRM8</t>
+          <t>ATP5PO;CYB5A;ATP6V0C;NDUFA2;UQCR10;NDUFB8;NDUFS7;NDUFS8;ATP5MG;NDUFB1;MRPS15;POLR2F;MPC1;ATP5MF;TIMM8B;MTRF1;COX5B;ATP5ME;NDUFB7;NDUFB2;UQCR11;ATP6V1F;ECI1;ETFB;PHYH;ATP6V0B;GPX4;ATP5F1D;SURF1;NDUFA3;TIMM10;ECH1;ATP5MC1;BDH2;LDHB;NDUFA9;NDUFA7;MRPL34;ATP5PF;NDUFS6;ATP5PD;NDUFS3;NDUFB6;NDUFB5;SDHA;COX6C;TCIRG1;MRPL11;UQCRQ;COX8A;HTRA2;NDUFA6;NDUFA4;MTRR;NQO2;ATP5F1E;NDUFV1;RHOT2;SDHD;COX7A2;COX6B1;COX7B;NDUFB4;ACAT1;MRPS12;COX4I1;NDUFC2;HSD17B10;CYC1;COX6A1;ACADVL;FDX1;NDUFA1;SDHB;SUCLG1</t>
         </is>
       </c>
     </row>
@@ -2298,21 +2298,21 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1.134</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.796</v>
+        <v>0.791</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1.122</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.455</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.802</v>
+        <v>0.798</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2388,45 +2388,45 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Adipogenesis</t>
+          <t>IL-6/JAK/STAT3 Signaling</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>1.113</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.823</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>28/200</t>
+          <t>27/87</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11.40%</t>
+          <t>26.03%</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>LAMA4;COL15A1;COL4A1;IDH3A;MYLK;BAZ2A;GPHN;RREB1;SOWAHC;ELOVL6;ALDOA;ENPP2;FZD4;ITSN1;CHUK;GBE1;ABCA1;SSPN;ADCY6;ADIPOR2;GPAT4;G3BP2;ITIH5;SCARB1;DLAT;LPCAT3;GPD2;CCNG2</t>
+          <t>IL1R2;PTPN11;LEPR;PDGFC;IL18R1;CBL;TNFRSF21;CXCL1;ITGA4;IL2RA;IL7;CSF2RB;IL17RA;CXCL3;CD44;IL6;IL4R;IL1R1;STAT3;INHBE;IL1B;STAT1;OSMR;IL13RA1;A2M;IL15RA;ACVRL1</t>
         </is>
       </c>
     </row>
@@ -2438,45 +2438,45 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IL-6/JAK/STAT3 Signaling</t>
+          <t>Adipogenesis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1.049</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.823</v>
+        <v>0.835</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>27/87</t>
+          <t>28/200</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>26.03%</t>
+          <t>11.40%</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>IL1R2;PTPN11;LEPR;PDGFC;IL18R1;CBL;TNFRSF21;CXCL1;ITGA4;IL2RA;IL7;CSF2RB;IL17RA;CXCL3;CD44;IL6;IL4R;IL1R1;STAT3;INHBE;IL1B;STAT1;OSMR;IL13RA1;A2M;IL15RA;ACVRL1</t>
+          <t>LAMA4;COL15A1;COL4A1;IDH3A;MYLK;BAZ2A;GPHN;RREB1;SOWAHC;ELOVL6;ALDOA;ENPP2;FZD4;ITSN1;CHUK;GBE1;ABCA1;SSPN;ADCY6;ADIPOR2;GPAT4;G3BP2;ITIH5;SCARB1;DLAT;LPCAT3;GPD2;CCNG2</t>
         </is>
       </c>
     </row>
@@ -2498,21 +2498,21 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>0.606</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.874</v>
+        <v>0.894</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2548,21 +2548,21 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>0.919</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>0.535</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.623</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.883</v>
+        <v>0.902</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2588,45 +2588,45 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pperoxisome</t>
+          <t>Bile Acid Metabolism</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.234</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>0.902</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.567</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>0.626</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.889</v>
+        <v>0.908</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18/103</t>
+          <t>20/111</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>18.98%</t>
+          <t>15.90%</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>IDE;ABCB4;ACSL4;SLC23A2;ATXN1;SEMA3C;SMARCC1;CTPS1;CLN6;VPS4B;LONP2;TOP2A;DLG4;ABCB1;PEX5;MLYCD;CLN8;FADS1</t>
+          <t>DIO2;BMP6;SLC23A2;NEDD4;ATXN1;PFKM;FADS2;ABCA1;SULT1B1;PEX1;BCAR3;PEX26;LONP2;AR;ABCA6;CYP7B1;GCLM;TFCP2L1;ABCA2;MLYCD</t>
         </is>
       </c>
     </row>
@@ -2638,45 +2638,45 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bile Acid Metabolism</t>
+          <t>Pperoxisome</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>0.898</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.89</v>
+        <v>0.909</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20/111</t>
+          <t>18/103</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15.90%</t>
+          <t>18.98%</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DIO2;BMP6;SLC23A2;NEDD4;ATXN1;PFKM;FADS2;ABCA1;SULT1B1;PEX1;BCAR3;PEX26;LONP2;AR;ABCA6;CYP7B1;GCLM;TFCP2L1;ABCA2;MLYCD</t>
+          <t>IDE;ABCB4;ACSL4;SLC23A2;ATXN1;SEMA3C;SMARCC1;CTPS1;CLN6;VPS4B;LONP2;TOP2A;DLG4;ABCB1;PEX5;MLYCD;CLN8;FADS1</t>
         </is>
       </c>
     </row>
@@ -2698,21 +2698,21 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.841</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.621</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.917</v>
+        <v>0.924</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.817</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>0.604</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.770</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.676</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.718</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.93</v>
+        <v>0.945</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-0.719</t>
+          <t>-0.738</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>0.661</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.716</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.9726720647773279</v>
+        <v>0.9663951120162932</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>0.542</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>0.844</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>0.916</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.975</v>
+        <v>0.979</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.889</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>0.956</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.981</v>
+        <v>0.984</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
